--- a/data/trans_dic/P44A$analisis-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P44A$analisis-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 45,8</t>
+          <t>4,96; 45,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,5; 47,51</t>
+          <t>10,77; 48,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 17,24</t>
+          <t>6,88; 17,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 67,67</t>
+          <t>8,33; 65,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,94</t>
+          <t>0,0; 65,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 13,09</t>
+          <t>3,7; 12,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,46; 45,1</t>
+          <t>12,65; 46,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,76; 43,26</t>
+          <t>13,36; 44,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 14,35</t>
+          <t>6,77; 13,88</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,51</t>
+          <t>0,0; 36,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,19; 76,81</t>
+          <t>35,78; 75,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,85; 24,38</t>
+          <t>8,63; 23,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,93; 89,83</t>
+          <t>27,73; 90,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 15,62</t>
+          <t>4,19; 16,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 52,41</t>
+          <t>12,88; 52,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,27; 65,87</t>
+          <t>29,72; 64,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 19,01</t>
+          <t>8,12; 18,8</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,49; 58,16</t>
+          <t>14,53; 56,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,52; 55,72</t>
+          <t>17,17; 55,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,33; 95,58</t>
+          <t>14,02; 93,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,81</t>
+          <t>0,0; 46,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,79</t>
+          <t>0,0; 55,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 13,61</t>
+          <t>1,65; 14,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,94; 46,57</t>
+          <t>15,43; 47,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,27; 48,14</t>
+          <t>17,38; 49,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,46; 92,28</t>
+          <t>11,59; 92,7</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,77; 77,36</t>
+          <t>41,78; 77,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,19; 44,13</t>
+          <t>19,27; 43,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 19,9</t>
+          <t>9,92; 19,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,54; 75,01</t>
+          <t>22,35; 74,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,3; 55,49</t>
+          <t>10,74; 53,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 13,82</t>
+          <t>4,72; 13,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,02; 72,86</t>
+          <t>43,04; 72,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,13; 40,33</t>
+          <t>19,82; 40,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,03; 16,06</t>
+          <t>9,13; 16,64</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,8</t>
+          <t>0,0; 62,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,88; 61,32</t>
+          <t>22,31; 62,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,76; 20,52</t>
+          <t>5,33; 20,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 40,91</t>
+          <t>7,61; 41,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,06; 68,97</t>
+          <t>27,26; 70,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,49; 20,3</t>
+          <t>10,25; 20,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,02; 39,2</t>
+          <t>9,04; 38,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,03; 60,79</t>
+          <t>32,61; 59,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,1; 18,38</t>
+          <t>10,02; 18,22</t>
         </is>
       </c>
     </row>
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,12; 50,01</t>
+          <t>16,31; 50,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,64; 53,2</t>
+          <t>20,64; 54,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,91; 20,51</t>
+          <t>10,39; 20,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,12; 50,01</t>
+          <t>16,31; 50,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,64; 53,2</t>
+          <t>20,64; 54,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,34; 19,64</t>
+          <t>10,36; 19,78</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,99; 47,61</t>
+          <t>27,93; 49,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29,1; 44,33</t>
+          <t>29,47; 44,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,85; 77,4</t>
+          <t>12,59; 74,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,07; 42,6</t>
+          <t>24,49; 42,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,77; 43,07</t>
+          <t>23,9; 42,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,33; 13,7</t>
+          <t>9,28; 13,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,26; 42,05</t>
+          <t>27,97; 41,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,69; 41,41</t>
+          <t>28,9; 41,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,06; 60,74</t>
+          <t>12,02; 60,97</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1031; 8773</t>
+          <t>949; 8730</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4177; 14697</t>
+          <t>3332; 14862</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8705; 22116</t>
+          <t>8829; 22748</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1175; 9050</t>
+          <t>1114; 8697</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7090</t>
+          <t>0; 7317</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2459; 9641</t>
+          <t>2727; 9379</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4379; 14672</t>
+          <t>4114; 15072</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5782; 18182</t>
+          <t>5614; 18744</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14020; 28985</t>
+          <t>13682; 28031</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6575</t>
+          <t>0; 5919</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9483; 20698</t>
+          <t>9642; 20260</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7328; 20186</t>
+          <t>7145; 19770</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2321; 7463</t>
+          <t>2304; 7488</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1625</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1899; 7651</t>
+          <t>2051; 8089</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3173; 12860</t>
+          <t>3160; 12918</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9442; 21252</t>
+          <t>9590; 20840</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10599; 25049</t>
+          <t>10705; 24780</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5123; 17033</t>
+          <t>4256; 16676</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5117; 16273</t>
+          <t>5015; 16082</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47288; 315478</t>
+          <t>46260; 309282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5104</t>
+          <t>0; 5116</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4103</t>
+          <t>0; 4118</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>533; 4436</t>
+          <t>538; 4721</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5604; 18715</t>
+          <t>6203; 18902</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5949; 17601</t>
+          <t>6353; 17985</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41563; 334660</t>
+          <t>42035; 336161</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15857; 28022</t>
+          <t>15136; 28033</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8979; 21781</t>
+          <t>9513; 21338</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15995; 31673</t>
+          <t>15782; 31783</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3266; 10866</t>
+          <t>3238; 10830</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3232; 13487</t>
+          <t>2610; 12933</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3832; 11812</t>
+          <t>4032; 11848</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22321; 36946</t>
+          <t>21827; 36953</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14093; 29705</t>
+          <t>14603; 29959</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22094; 39298</t>
+          <t>22345; 40702</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5234</t>
+          <t>0; 5268</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5317; 14251</t>
+          <t>5185; 14429</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3829; 13648</t>
+          <t>3543; 13687</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2042; 11018</t>
+          <t>2050; 11081</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8240; 18907</t>
+          <t>7472; 19365</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11621; 22492</t>
+          <t>11360; 22195</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3192; 13879</t>
+          <t>3199; 13691</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16225; 30793</t>
+          <t>16517; 29999</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17913; 32594</t>
+          <t>17769; 32306</t>
         </is>
       </c>
     </row>
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1027</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5153; 15984</t>
+          <t>5213; 16085</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8142; 20983</t>
+          <t>8140; 21623</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13066; 24564</t>
+          <t>12441; 24366</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5153; 15984</t>
+          <t>5213; 16085</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8142; 20983</t>
+          <t>8140; 21623</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12785; 24291</t>
+          <t>12812; 24463</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30607; 52072</t>
+          <t>30546; 53643</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>46469; 70793</t>
+          <t>47067; 71353</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99008; 596502</t>
+          <t>97042; 576780</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24440; 45135</t>
+          <t>25952; 44986</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>27314; 49495</t>
+          <t>27461; 49228</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43972; 64559</t>
+          <t>43758; 63466</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>60844; 90540</t>
+          <t>60227; 89149</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>81520; 113707</t>
+          <t>79372; 113137</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>149792; 754429</t>
+          <t>149337; 757237</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$analisis-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P44A$analisis-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 45,58</t>
+          <t>5,55; 47,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,77; 48,04</t>
+          <t>13,42; 47,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 17,73</t>
+          <t>6,68; 17,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 65,03</t>
+          <t>8,33; 64,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,98</t>
+          <t>0,0; 65,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 12,73</t>
+          <t>4,6; 14,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,65; 46,33</t>
+          <t>13,05; 47,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,36; 44,6</t>
+          <t>14,5; 43,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 13,88</t>
+          <t>6,92; 14,19</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -788,22 +788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,47</t>
+          <t>0,0; 34,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,78; 75,18</t>
+          <t>32,57; 75,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 23,88</t>
+          <t>8,55; 23,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,73; 90,13</t>
+          <t>27,76; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 16,51</t>
+          <t>4,64; 16,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,88; 52,65</t>
+          <t>12,18; 52,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,72; 64,59</t>
+          <t>28,92; 64,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 18,8</t>
+          <t>8,47; 19,27</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 56,94</t>
+          <t>17,44; 58,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,17; 55,07</t>
+          <t>17,13; 53,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,02; 93,71</t>
+          <t>10,53; 26,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,93</t>
+          <t>0,0; 52,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,99</t>
+          <t>0,0; 63,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 14,49</t>
+          <t>0,0; 14,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,43; 47,03</t>
+          <t>15,77; 49,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,38; 49,2</t>
+          <t>17,62; 47,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,59; 92,7</t>
+          <t>9,22; 20,81</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,78; 77,39</t>
+          <t>44,89; 79,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,27; 43,23</t>
+          <t>17,92; 43,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,92; 19,97</t>
+          <t>10,03; 19,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,35; 74,76</t>
+          <t>22,25; 73,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,74; 53,21</t>
+          <t>13,26; 54,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 13,86</t>
+          <t>4,81; 14,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,04; 72,87</t>
+          <t>43,24; 70,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,82; 40,67</t>
+          <t>20,28; 42,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,13; 16,64</t>
+          <t>9,14; 16,04</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,19</t>
+          <t>0,0; 62,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,31; 62,08</t>
+          <t>24,39; 59,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,33; 20,58</t>
+          <t>5,2; 19,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,61; 41,15</t>
+          <t>7,25; 40,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,26; 70,65</t>
+          <t>29,03; 68,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,25; 20,03</t>
+          <t>10,39; 20,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,04; 38,67</t>
+          <t>9,29; 37,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,61; 59,23</t>
+          <t>31,23; 60,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,02; 18,22</t>
+          <t>9,46; 17,35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -1243,32 +1243,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,31; 50,33</t>
+          <t>18,48; 52,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,64; 54,82</t>
+          <t>21,06; 53,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,39; 20,34</t>
+          <t>11,07; 20,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,31; 50,33</t>
+          <t>18,48; 52,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,64; 54,82</t>
+          <t>21,06; 53,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,36; 19,78</t>
+          <t>10,48; 20,19</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,93; 49,05</t>
+          <t>28,55; 47,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29,47; 44,68</t>
+          <t>29,02; 44,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,59; 74,84</t>
+          <t>10,95; 16,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,49; 42,46</t>
+          <t>22,49; 41,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,9; 42,84</t>
+          <t>24,38; 43,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,28; 13,46</t>
+          <t>9,61; 13,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,97; 41,4</t>
+          <t>27,93; 41,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,9; 41,2</t>
+          <t>29,46; 41,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,02; 60,97</t>
+          <t>10,93; 14,47</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>15002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20046</t>
+          <t>22214</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>949; 8730</t>
+          <t>1063; 9083</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3332; 14862</t>
+          <t>4151; 14731</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8829; 22748</t>
+          <t>9104; 23314</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1114; 8697</t>
+          <t>1114; 8572</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7317</t>
+          <t>0; 7256</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2727; 9379</t>
+          <t>3824; 12360</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4114; 15072</t>
+          <t>4245; 15313</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5614; 18744</t>
+          <t>6095; 18306</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13682; 28031</t>
+          <t>15190; 31130</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>17941</t>
         </is>
       </c>
     </row>
@@ -1802,22 +1802,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5919</t>
+          <t>0; 5642</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9642; 20260</t>
+          <t>8778; 20366</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7145; 19770</t>
+          <t>7354; 20168</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2304; 7488</t>
+          <t>2307; 8308</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1827,22 +1827,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2051; 8089</t>
+          <t>2550; 9039</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3160; 12918</t>
+          <t>2988; 12805</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9590; 20840</t>
+          <t>9330; 20743</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10705; 24780</t>
+          <t>11943; 27169</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>258477</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>260281</t>
+          <t>17608</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4256; 16676</t>
+          <t>5107; 17136</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5015; 16082</t>
+          <t>5004; 15514</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46260; 309282</t>
+          <t>9629; 23875</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5116</t>
+          <t>0; 5735</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4118</t>
+          <t>0; 4698</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>538; 4721</t>
+          <t>0; 5067</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6203; 18902</t>
+          <t>6340; 19823</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6353; 17985</t>
+          <t>6441; 17335</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42035; 336161</t>
+          <t>11752; 26518</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22952</t>
+          <t>24917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>33408</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15136; 28033</t>
+          <t>16262; 28723</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9513; 21338</t>
+          <t>8845; 21324</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15782; 31783</t>
+          <t>17446; 34685</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3238; 10830</t>
+          <t>3223; 10628</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2610; 12933</t>
+          <t>3223; 13214</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4032; 11848</t>
+          <t>4498; 13845</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21827; 36953</t>
+          <t>21925; 36000</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14603; 29959</t>
+          <t>14941; 31545</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22345; 40702</t>
+          <t>24441; 42905</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24007</t>
+          <t>25267</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5268</t>
+          <t>0; 5255</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5185; 14429</t>
+          <t>5668; 13937</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3543; 13687</t>
+          <t>3795; 13933</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2050; 11081</t>
+          <t>1952; 10968</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7472; 19365</t>
+          <t>7958; 18709</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11360; 22195</t>
+          <t>12474; 24354</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3199; 13691</t>
+          <t>3288; 13383</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16517; 29999</t>
+          <t>15821; 30395</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17769; 32306</t>
+          <t>18259; 33486</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>20437</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>20437</t>
         </is>
       </c>
     </row>
@@ -2469,32 +2469,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5213; 16085</t>
+          <t>5905; 16734</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8140; 21623</t>
+          <t>8305; 20928</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12441; 24366</t>
+          <t>14638; 27397</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5213; 16085</t>
+          <t>5905; 16734</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8140; 21623</t>
+          <t>8305; 20928</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12812; 24463</t>
+          <t>14259; 27473</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>315969</t>
+          <t>76147</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53192</t>
+          <t>60727</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>369161</t>
+          <t>136875</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30546; 53643</t>
+          <t>31229; 52413</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>47067; 71353</t>
+          <t>46341; 70995</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97042; 576780</t>
+          <t>61808; 91046</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25952; 44986</t>
+          <t>23835; 44228</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>27461; 49228</t>
+          <t>28013; 49795</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43758; 63466</t>
+          <t>49944; 72705</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>60227; 89149</t>
+          <t>60141; 89037</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>79372; 113137</t>
+          <t>80892; 114136</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>149337; 757237</t>
+          <t>118470; 156912</t>
         </is>
       </c>
     </row>
